--- a/src/moodys_datahub/data/date_cols.xlsx
+++ b/src/moodys_datahub/data/date_cols.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_lib_cbs_dk/Documents/Desktop/moody-s_datahub/moodys_datahub/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="11_2BB1D69C5B70DB28EB3B2311592620F659D1E438" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{416F1F40-E8EF-4244-997B-C54C790A0975}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="11_2BB1D69C5B70DB28EB3B2311592620F659D1E438" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012068E7-4636-400A-921F-57618A59AFA3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Ark1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -189,51 +189,21 @@
     <t>segment_data</t>
   </si>
   <si>
-    <t>banks_global_financials_and_ratios_eur_interim</t>
-  </si>
-  <si>
     <t>banks_global_financials_and_ratios_interim</t>
   </si>
   <si>
-    <t>banks_global_financials_and_ratios_usd_interim</t>
-  </si>
-  <si>
-    <t>cash_flow_non_us_industries_eur_interim</t>
-  </si>
-  <si>
     <t>cash_flow_non_us_industries_interim</t>
   </si>
   <si>
-    <t>cash_flow_non_us_industries_usd_interim</t>
-  </si>
-  <si>
-    <t>cash_flow_us_industries_eur_interim</t>
-  </si>
-  <si>
     <t>cash_flow_us_industries_interim</t>
   </si>
   <si>
-    <t>cash_flow_us_industries_usd_interim</t>
-  </si>
-  <si>
-    <t>detailed_format_industries_eur_interim</t>
-  </si>
-  <si>
     <t>detailed_format_industries_interim</t>
   </si>
   <si>
-    <t>detailed_format_industries_usd_interim</t>
-  </si>
-  <si>
-    <t>industry_global_financials_and_ratios_eur_interim</t>
-  </si>
-  <si>
     <t>industry_global_financials_and_ratios_interim</t>
   </si>
   <si>
-    <t>industry_global_financials_and_ratios_usd_interim</t>
-  </si>
-  <si>
     <t>Financials History (Semi-Annual)</t>
   </si>
   <si>
@@ -544,6 +514,36 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>banks_global_financials_and_ratios_interim_eur</t>
+  </si>
+  <si>
+    <t>cash_flow_non_us_industries_interim_eur</t>
+  </si>
+  <si>
+    <t>cash_flow_us_industries_interim_eur</t>
+  </si>
+  <si>
+    <t>detailed_format_industries_interim_eur</t>
+  </si>
+  <si>
+    <t>industry_global_financials_and_ratios_interim_eur</t>
+  </si>
+  <si>
+    <t>industry_global_financials_and_ratios_interim_usd</t>
+  </si>
+  <si>
+    <t>banks_global_financials_and_ratios_interim_usd</t>
+  </si>
+  <si>
+    <t>cash_flow_non_us_industries_interim_usd</t>
+  </si>
+  <si>
+    <t>cash_flow_us_industries_interim_usd</t>
+  </si>
+  <si>
+    <t>detailed_format_industries_interim_usd</t>
   </si>
 </sst>
 </file>
@@ -938,16 +938,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -955,7 +955,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -969,7 +969,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -983,7 +983,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -997,7 +997,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1025,7 +1025,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -1039,7 +1039,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -1053,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1067,7 +1067,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1260,86 +1260,86 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1361,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>5</v>
@@ -1375,7 +1375,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>5</v>
@@ -1389,7 +1389,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
@@ -1403,7 +1403,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>5</v>
@@ -1417,7 +1417,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>55</v>
+        <v>166</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
@@ -1431,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>5</v>
@@ -1445,7 +1445,7 @@
         <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>5</v>
@@ -1459,7 +1459,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>5</v>
@@ -1473,7 +1473,7 @@
         <v>7</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>5</v>
@@ -1487,7 +1487,7 @@
         <v>7</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>5</v>
@@ -1501,7 +1501,7 @@
         <v>7</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>7</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>5</v>
@@ -1529,7 +1529,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>5</v>
@@ -1543,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>5</v>
@@ -1557,7 +1557,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>5</v>
@@ -1571,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>5</v>
@@ -1585,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>5</v>
@@ -1599,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>17</v>
@@ -1669,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>24</v>
@@ -1826,15 +1826,15 @@
         <v>49</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>40</v>
@@ -1843,12 +1843,12 @@
         <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>41</v>
@@ -1857,12 +1857,12 @@
         <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>42</v>
@@ -1871,12 +1871,12 @@
         <v>5</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>43</v>
@@ -1885,12 +1885,12 @@
         <v>5</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>44</v>
@@ -1899,12 +1899,12 @@
         <v>5</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>45</v>
@@ -1913,12 +1913,12 @@
         <v>5</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>46</v>
@@ -1927,12 +1927,12 @@
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>47</v>
@@ -1941,12 +1941,12 @@
         <v>5</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>48</v>
@@ -1955,21 +1955,21 @@
         <v>5</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1977,7 +1977,7 @@
         <v>27</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>14</v>
@@ -1991,7 +1991,7 @@
         <v>27</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>14</v>
@@ -2005,7 +2005,7 @@
         <v>27</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>14</v>
@@ -2019,7 +2019,7 @@
         <v>27</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>14</v>
@@ -2033,7 +2033,7 @@
         <v>27</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>14</v>
@@ -2047,7 +2047,7 @@
         <v>27</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>14</v>
@@ -2061,7 +2061,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>14</v>
@@ -2075,7 +2075,7 @@
         <v>27</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>14</v>
@@ -2089,7 +2089,7 @@
         <v>27</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>14</v>
@@ -2103,7 +2103,7 @@
         <v>27</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>14</v>
@@ -2117,7 +2117,7 @@
         <v>27</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>14</v>
@@ -2131,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>14</v>
@@ -2145,7 +2145,7 @@
         <v>27</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>14</v>
@@ -2159,7 +2159,7 @@
         <v>27</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>14</v>
@@ -2173,7 +2173,7 @@
         <v>27</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>14</v>
@@ -2187,7 +2187,7 @@
         <v>27</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>14</v>
@@ -2313,13 +2313,13 @@
         <v>10</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2327,13 +2327,13 @@
         <v>10</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -2341,13 +2341,13 @@
         <v>10</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C102" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D102" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -2355,13 +2355,13 @@
         <v>10</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
+        <v>136</v>
+      </c>
+      <c r="D103" t="s">
         <v>146</v>
-      </c>
-      <c r="D103" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2369,13 +2369,13 @@
         <v>10</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C104" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D104" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -2383,13 +2383,13 @@
         <v>10</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D105" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2397,13 +2397,13 @@
         <v>10</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C106" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D106" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2411,13 +2411,13 @@
         <v>10</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C107" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D107" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -2425,13 +2425,13 @@
         <v>10</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D108" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -2439,273 +2439,273 @@
         <v>10</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D110" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D112" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D113" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D117" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="C120" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D122" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D123" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D127" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B128" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C128" t="s">
         <v>14</v>
@@ -2716,20 +2716,20 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B129" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C129" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D129" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D127" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:D129" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D127">
       <sortCondition ref="A1:A127"/>
     </sortState>

--- a/src/moodys_datahub/data/date_cols.xlsx
+++ b/src/moodys_datahub/data/date_cols.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_libas_cbs_dk/Documents/Desktop/moody-s_datahub/src/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="11_2BB1D69C5B70DB28EB3B2311592620F659D1E438" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{012068E7-4636-400A-921F-57618A59AFA3}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="11_2BB1D69C5B70DB28EB3B2311592620F659D1E438" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC093CC2-8436-4053-A279-2F94C68F6986}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="170">
   <si>
     <t>Data Product</t>
   </si>
@@ -544,6 +544,9 @@
   </si>
   <si>
     <t>detailed_format_industries_interim_usd</t>
+  </si>
+  <si>
+    <t>status_history</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1280,7 @@
         <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>119</v>
